--- a/df.xlsx
+++ b/df.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other(Seed_variety)</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other(Seed_variety)</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
